--- a/Figure_Plot/figure_plot_S1/settings_sequence.xlsx
+++ b/Figure_Plot/figure_plot_S1/settings_sequence.xlsx
@@ -1166,73 +1166,73 @@
         <v>1.54</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.8733333333333333</v>
+        <v>1.913333333333333</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2066666666666668</v>
+        <v>1.246666666666666</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.7466666666666668</v>
+        <v>1.786666666666666</v>
       </c>
       <c r="H2" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.9933333333333332</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="M2" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="N2" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="O2" s="3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>1.153333333333333</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.4866666666666667</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="T2" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="U2" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="L2" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="N2" s="3" t="n">
+      <c r="V2" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="W2" s="3" t="n">
         <v>1.82</v>
       </c>
-      <c r="P2" s="3" t="n">
-        <v>1.153333333333333</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.4866666666666667</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S2" s="3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="T2" s="3" t="n">
-        <v>0.9199999999999999</v>
-      </c>
-      <c r="U2" s="3" t="n">
+      <c r="X2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="3" t="n">
         <v>1.46</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="Z2" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="W2" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X2" s="2" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Y2" s="3" t="n">
-        <v>0.6666666666666669</v>
-      </c>
-      <c r="Z2" s="2" t="n">
-        <v>0.2</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
@@ -1245,76 +1245,76 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.8733333333333333</v>
+        <v>1.913333333333333</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.2066666666666668</v>
+        <v>1.246666666666666</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.7466666666666668</v>
+        <v>1.786666666666666</v>
       </c>
       <c r="H3" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.9933333333333332</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="M3" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="N3" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="O3" s="3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>1.153333333333333</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.4866666666666667</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="T3" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="U3" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="L3" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="N3" s="3" t="n">
+      <c r="V3" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="W3" s="3" t="n">
         <v>1.82</v>
       </c>
-      <c r="P3" s="3" t="n">
-        <v>1.153333333333333</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.4866666666666667</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S3" s="3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>0.9199999999999999</v>
-      </c>
-      <c r="U3" s="3" t="n">
+      <c r="X3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>1.46</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="Z3" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="W3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" s="2" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Y3" s="3" t="n">
-        <v>0.6666666666666669</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0.2</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
@@ -1327,10 +1327,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>0.9199999999999999</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>1.46</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>2</v>
@@ -1339,64 +1339,64 @@
         <v>1.333333333333333</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.333333333333333</v>
+        <v>1.873333333333334</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.6666666666666669</v>
+        <v>1.206666666666667</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.9933333333333332</v>
+        <v>1.746666666666667</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.3266666666666667</v>
+        <v>1.080000000000001</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.8666666666666667</v>
+        <v>1.620000000000001</v>
       </c>
       <c r="L4" s="3" t="n">
+        <v>0.9533333333333339</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0.2866666666666673</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0.8266666666666673</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>1.366666666666667</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>1.906666666666667</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>1.240000000000001</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.573333333333334</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="M4" s="3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="N4" s="3" t="n">
+      <c r="T4" s="3" t="n">
+        <v>0.7400000000000004</v>
+      </c>
+      <c r="U4" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="O4" s="3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>1.153333333333333</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.4866666666666667</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.3799999999999999</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>0.9199999999999999</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="U4" s="3" t="n">
+      <c r="V4" s="3" t="n">
+        <v>1.820000000000001</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>1.460000000000002</v>
+      </c>
+      <c r="X4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="Y4" s="3" t="n">
+        <v>1.460000000000001</v>
+      </c>
+      <c r="Z4" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="X4" s="2" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>0.6666666666666669</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>0.2</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
@@ -1409,76 +1409,76 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1.373333333333333</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1.913333333333333</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1.246666666666666</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>1.786666666666666</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0.9933333333333332</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>1.819999999999999</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>1.153333333333333</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.4866666666666663</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>0.7400000000000004</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>1.280000000000001</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>1.820000000000002</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>1.46</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="Z5" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0.6666666666666669</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0.9933333333333332</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0.3266666666666667</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0.8666666666666667</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>1.153333333333333</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.4866666666666667</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>0.9199999999999999</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X5" s="2" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>0.6666666666666669</v>
-      </c>
-      <c r="Z5" s="2" t="n">
-        <v>0.2</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
@@ -1491,49 +1491,49 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>0.346666666666666</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1.54</v>
+        <v>0.8866666666666662</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1.839999999999999</v>
+        <v>1.426666666666666</v>
       </c>
       <c r="F6" s="3" t="n">
+        <v>0.7599999999999997</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="I6" s="3" t="n">
         <v>1.173333333333333</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>1.713333333333333</v>
-      </c>
-      <c r="H6" s="3" t="n">
+      <c r="J6" s="3" t="n">
+        <v>0.5066666666666664</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>1.046666666666666</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>1.586666666666666</v>
-      </c>
-      <c r="J6" s="3" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.3799999999999999</v>
+      </c>
+      <c r="M6" s="3" t="n">
         <v>0.9199999999999999</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="N6" s="3" t="n">
         <v>1.46</v>
       </c>
-      <c r="L6" s="3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M6" s="3" t="n">
+      <c r="O6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="N6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O6" s="2" t="n">
+      <c r="P6" s="3" t="n">
         <v>1.533333333333333</v>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="Q6" s="3" t="n">
         <v>0.8666666666666667</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.2</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>0.2</v>
@@ -1542,25 +1542,25 @@
         <v>0.74</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0.9199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="U6" s="3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>1.280000000000001</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>1.820000000000001</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>1.46</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="Z6" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X6" s="2" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>0.6666666666666669</v>
-      </c>
-      <c r="Z6" s="2" t="n">
-        <v>0.2</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
@@ -1573,76 +1573,76 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.54</v>
+        <v>0.873333333333333</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.839999999999999</v>
+        <v>1.413333333333333</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.173333333333333</v>
+        <v>0.7466666666666654</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.713333333333333</v>
+        <v>1.286666666666665</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.046666666666666</v>
+        <v>0.6199999999999987</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.586666666666666</v>
+        <v>1.159999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.9199999999999999</v>
+        <v>0.4933333333333322</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.46</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.46</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>2</v>
+        <v>0.9066666666666658</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>2</v>
+        <v>1.446666666666666</v>
       </c>
       <c r="O7" s="3" t="n">
+        <v>1.986666666666666</v>
+      </c>
+      <c r="P7" s="3" t="n">
         <v>1.533333333333333</v>
       </c>
-      <c r="P7" s="3" t="n">
+      <c r="Q7" s="3" t="n">
         <v>0.8666666666666667</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.2</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="S7" s="3" t="n">
+        <v>0.7400000000000002</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U7" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="T7" s="3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>1.82</v>
-      </c>
       <c r="V7" s="3" t="n">
+        <v>1.280000000000001</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>1.820000000000001</v>
+      </c>
+      <c r="X7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="Y7" s="3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z7" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="X7" s="2" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>0.6666666666666669</v>
-      </c>
-      <c r="Z7" s="2" t="n">
-        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1775,73 +1775,73 @@
         <v>-0.6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>-0.5111111111111111</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.6</v>
+        <v>0.0780000000000006</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>-0.6</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.4920000000000002</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>-0.6</v>
       </c>
       <c r="I2" s="3" t="n">
+        <v>0.5999999999999999</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>-0.4222222222222222</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="X2" s="3" t="n">
         <v>0.486</v>
       </c>
-      <c r="J2" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.258</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="S2" s="3" t="n">
-        <v>-0.1999999999999999</v>
-      </c>
-      <c r="T2" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="U2" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="X2" s="3" t="n">
-        <v>0.6</v>
-      </c>
       <c r="Y2" s="3" t="n">
-        <v>0.4200000000000002</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
@@ -1851,76 +1851,76 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.5111111111111111</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.6</v>
+        <v>0.0780000000000006</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>-0.6</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.4920000000000002</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>-0.6</v>
       </c>
       <c r="I3" s="3" t="n">
+        <v>0.5999999999999999</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>-0.4222222222222222</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="X3" s="3" t="n">
         <v>0.486</v>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.258</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="S3" s="3" t="n">
-        <v>-0.1999999999999999</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>0.6</v>
-      </c>
       <c r="Y3" s="3" t="n">
-        <v>0.4200000000000002</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
@@ -1930,28 +1930,28 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.5111111111111111</v>
+        <v>0.07200000000000006</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.6</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-0.3629629629629627</v>
+        <v>-0.6</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>-0.6</v>
@@ -1960,7 +1960,7 @@
         <v>0.6</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>-0.6</v>
+        <v>0.6</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.6</v>
@@ -1969,16 +1969,16 @@
         <v>-0.6</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.6</v>
+        <v>-0.6</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.09600000000000011</v>
+        <v>0.6</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>-0.6</v>
+        <v>0.3360000000000002</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>-0.6</v>
@@ -1987,19 +1987,19 @@
         <v>-0.6</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>0.6</v>
+        <v>0.3239999999999988</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>0.6</v>
+        <v>0.4859999999999988</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.4200000000000002</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
@@ -2009,28 +2009,28 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.5111111111111111</v>
+        <v>0.15</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>-0.6</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.3629629629629627</v>
+        <v>-0.6</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>-0.6</v>
@@ -2039,7 +2039,7 @@
         <v>0.6</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>-0.6</v>
+        <v>0.6</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>-0.6</v>
@@ -2048,19 +2048,19 @@
         <v>-0.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0.6</v>
+        <v>-0.6</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.258</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.4222222222222227</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.1999999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>-0.6</v>
@@ -2069,16 +2069,16 @@
         <v>-0.6</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>0.6</v>
+        <v>0.486</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.4200000000000002</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
@@ -2088,16 +2088,16 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>0.5880000000000005</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>-0.6</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.3333333333333326</v>
+        <v>-0.6</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5999999999999998</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>-0.6</v>
@@ -2109,37 +2109,37 @@
         <v>-0.6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>-0.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>-0.6</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.4200000000000001</v>
+        <v>-0.6</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.6</v>
+        <v>0.4199999999999999</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>-0.6</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.1999999999999999</v>
+        <v>0.486</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>-0.6</v>
@@ -2148,16 +2148,16 @@
         <v>-0.6</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.6</v>
+        <v>0.486</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.4200000000000002</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
@@ -2167,13 +2167,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.6</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>-0.3333333333333326</v>
+        <v>-0.6</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.6</v>
@@ -2194,49 +2194,49 @@
         <v>-0.6</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>-0.6</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.4200000000000001</v>
+        <v>-0.6</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.6</v>
+        <v>0.4079999999999993</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>-0.6</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.6</v>
+        <v>0.4860000000000001</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>-0.6</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>-0.1999999999999999</v>
+        <v>-0.6</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>0.6</v>
+        <v>0.486</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.4200000000000002</v>
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
